--- a/datos/Equivalencias_MYC.xlsx
+++ b/datos/Equivalencias_MYC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Consumo_horas_educacion_secundaria\datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6530FC1B-393E-4A97-95D0-86462C733CF2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4211859-762D-4736-9C2C-74A66C03571F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1767,26 +1767,26 @@
       <c r="D35" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="E35" s="3">
-        <v>3064</v>
+      <c r="E35" s="7">
+        <v>3215</v>
       </c>
       <c r="F35" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G35" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="H35" s="6" t="s">
-        <v>18</v>
+      <c r="G35" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="H35" s="7" t="s">
+        <v>31</v>
       </c>
       <c r="I35" s="6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J35" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="K35" s="6">
-        <v>3215</v>
+      <c r="K35" s="7">
+        <v>3064</v>
       </c>
       <c r="L35" s="6" t="s">
         <v>15</v>
